--- a/src/nodes/P/compressor_stage_1_blade_rotor_coordinates_lattice.xlsx
+++ b/src/nodes/P/compressor_stage_1_blade_rotor_coordinates_lattice.xlsx
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-71.164529458085141</v>
+        <v>-71.219253947015346</v>
       </c>
       <c r="B1">
-        <v>42.382220293917953</v>
+        <v>42.297850866627549</v>
       </c>
       <c r="C1">
         <v>592.998505179033</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-67.198817232292939</v>
+        <v>-67.309306512663824</v>
       </c>
       <c r="B2">
-        <v>40.89135696771303</v>
+        <v>40.721014265773739</v>
       </c>
       <c r="C2">
         <v>592.998505179033</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-63.271313649140886</v>
+        <v>-63.431838816669512</v>
       </c>
       <c r="B3">
-        <v>39.341586900483989</v>
+        <v>39.0941032470988</v>
       </c>
       <c r="C3">
         <v>592.998505179033</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-59.371399544213233</v>
+        <v>-59.57861632457611</v>
       </c>
       <c r="B4">
-        <v>37.749281790488169</v>
+        <v>37.429813095102595</v>
       </c>
       <c r="C4">
         <v>592.998505179033</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-55.488455753094343</v>
+        <v>-55.741404501927335</v>
       </c>
       <c r="B5">
-        <v>36.13081333598295</v>
+        <v>35.740839094285072</v>
       </c>
       <c r="C5">
         <v>592.998505179033</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-51.616381518421058</v>
+        <v>-51.915470703583296</v>
       </c>
       <c r="B6">
-        <v>34.49558715070409</v>
+        <v>34.0344776226997</v>
       </c>
       <c r="C6">
         <v>592.998505179033</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-47.767149711040474</v>
+        <v>-48.110089841669812</v>
       </c>
       <c r="B7">
-        <v>32.825144510300994</v>
+        <v>32.296429432614453</v>
       </c>
       <c r="C7">
         <v>592.998505179033</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-43.953368283585995</v>
+        <v>-44.335029201453153</v>
       </c>
       <c r="B8">
-        <v>31.100047576910235</v>
+        <v>30.5116361784841</v>
       </c>
       <c r="C8">
         <v>592.998505179033</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-40.172111887626187</v>
+        <v>-40.588018003495812</v>
       </c>
       <c r="B9">
-        <v>29.324806396703256</v>
+        <v>28.683598749296163</v>
       </c>
       <c r="C9">
         <v>592.998505179033</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-36.417668053069626</v>
+        <v>-36.864625660743911</v>
       </c>
       <c r="B10">
-        <v>27.508227956085019</v>
+        <v>26.819147836384719</v>
       </c>
       <c r="C10">
         <v>592.998505179033</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-32.688709124249911</v>
+        <v>-33.163820420381789</v>
       </c>
       <c r="B11">
-        <v>25.652359118359378</v>
+        <v>24.919874105937122</v>
       </c>
       <c r="C11">
         <v>592.998505179033</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-28.985003649106904</v>
+        <v>-29.485420238153349</v>
       </c>
       <c r="B12">
-        <v>23.757556716054893</v>
+        <v>22.986058217854072</v>
       </c>
       <c r="C12">
         <v>592.998505179033</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-25.306320175580439</v>
+        <v>-25.829243069802484</v>
       </c>
       <c r="B13">
-        <v>21.824177581700166</v>
+        <v>21.017980832036283</v>
       </c>
       <c r="C13">
         <v>592.998505179033</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-21.652413227061562</v>
+        <v>-22.195096185396384</v>
       </c>
       <c r="B14">
-        <v>19.852600169645644</v>
+        <v>19.015939082625536</v>
       </c>
       <c r="C14">
         <v>592.998505179033</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-18.022981228746026</v>
+        <v>-18.582744112295369</v>
       </c>
       <c r="B15">
-        <v>17.843289421529249</v>
+        <v>16.980296000728021</v>
       </c>
       <c r="C15">
         <v>592.998505179033</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-14.41770858128079</v>
+        <v>-14.991940692183068</v>
       </c>
       <c r="B16">
-        <v>15.796731900810812</v>
+        <v>14.911431091691009</v>
       </c>
       <c r="C16">
         <v>592.998505179033</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-10.836279685312787</v>
+        <v>-11.42243976674308</v>
       </c>
       <c r="B17">
-        <v>13.713414170950124</v>
+        <v>12.809723860861768</v>
       </c>
       <c r="C17">
         <v>592.998505179033</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-7.2785045980231811</v>
+        <v>-7.87409273514599</v>
       </c>
       <c r="B18">
-        <v>11.593629069160599</v>
+        <v>10.675403407992876</v>
       </c>
       <c r="C18">
         <v>592.998505179033</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.7446960027299858</v>
+        <v>-4.3471412265102121</v>
       </c>
       <c r="B19">
-        <v>9.4368945276700611</v>
+        <v>8.5080972104580983</v>
       </c>
       <c r="C19">
         <v>592.998505179033</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-0.23529223928538123</v>
+        <v>-0.84192442744107943</v>
       </c>
       <c r="B20">
-        <v>7.2425347524599086</v>
+        <v>6.3072823400364717</v>
       </c>
       <c r="C20">
         <v>592.998505179033</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>3.2492683524584067</v>
+        <v>2.6412184754560277</v>
       </c>
       <c r="B21">
-        <v>5.00987394951158</v>
+        <v>4.0724358685070623</v>
       </c>
       <c r="C21">
         <v>592.998505179033</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>6.7086935459332606</v>
+        <v>6.1020613577775622</v>
       </c>
       <c r="B22">
-        <v>2.7384615894793294</v>
+        <v>1.8032091770558918</v>
       </c>
       <c r="C22">
         <v>592.998505179033</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>10.14327556770731</v>
+        <v>9.5408303439270838</v>
       </c>
       <c r="B23">
-        <v>0.42874820170889316</v>
+        <v>-0.50004911550306874</v>
       </c>
       <c r="C23">
         <v>592.998505179033</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>13.553452757632746</v>
+        <v>12.957864620509936</v>
       </c>
       <c r="B24">
-        <v>-1.9185904197811425</v>
+        <v>-2.8368160809488638</v>
       </c>
       <c r="C24">
         <v>592.998505179033</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>16.939663455561792</v>
+        <v>16.3535033741315</v>
       </c>
       <c r="B25">
-        <v>-4.3028784809722058</v>
+        <v>-5.2065687910605627</v>
       </c>
       <c r="C25">
         <v>592.998505179033</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>20.302220344812433</v>
+        <v>19.727988233910157</v>
       </c>
       <c r="B26">
-        <v>-6.723633914092094</v>
+        <v>-7.6089347232119</v>
       </c>
       <c r="C26">
         <v>592.998505179033</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>23.640933482565838</v>
+        <v>23.081170599016495</v>
       </c>
       <c r="B27">
-        <v>-9.1811495563542369</v>
+        <v>-10.04414297715547</v>
       </c>
       <c r="C27">
         <v>592.998505179033</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>26.955487269468936</v>
+        <v>26.412804311134117</v>
       </c>
       <c r="B28">
-        <v>-11.675911971218426</v>
+        <v>-12.512573058238528</v>
       </c>
       <c r="C28">
         <v>592.998505179033</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>30.245566106168706</v>
+        <v>29.722643211946657</v>
       </c>
       <c r="B29">
-        <v>-14.208407722144482</v>
+        <v>-15.014604471808369</v>
       </c>
       <c r="C29">
         <v>592.998505179033</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>33.5108684178609</v>
+        <v>33.010451828814446</v>
       </c>
       <c r="B30">
-        <v>-16.779101750770341</v>
+        <v>-17.550600248971158</v>
       </c>
       <c r="C30">
         <v>592.998505179033</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>36.751148727936517</v>
+        <v>36.276037431804639</v>
       </c>
       <c r="B31">
-        <v>-19.388372511446427</v>
+        <v>-20.120857523868683</v>
       </c>
       <c r="C31">
         <v>592.998505179033</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>39.96617558433546</v>
+        <v>39.519217976661174</v>
       </c>
       <c r="B32">
-        <v>-22.036576836701375</v>
+        <v>-22.725656956401679</v>
       </c>
       <c r="C32">
         <v>592.998505179033</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>43.155717534997542</v>
+        <v>42.739811419127918</v>
       </c>
       <c r="B33">
-        <v>-24.724071559063717</v>
+        <v>-25.365279206470806</v>
       </c>
       <c r="C33">
         <v>592.998505179033</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>46.318446924256364</v>
+        <v>45.936786006389212</v>
       </c>
       <c r="B34">
-        <v>-27.452903541837319</v>
+        <v>-28.041314940263451</v>
       </c>
       <c r="C34">
         <v>592.998505179033</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>49.448651282020549</v>
+        <v>49.105711151391212</v>
       </c>
       <c r="B35">
-        <v>-30.231879771427142</v>
+        <v>-30.760594849113691</v>
       </c>
       <c r="C35">
         <v>592.998505179033</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>52.543405259858595</v>
+        <v>52.244316074696357</v>
       </c>
       <c r="B36">
-        <v>-33.065510294004625</v>
+        <v>-33.526619822009017</v>
       </c>
       <c r="C36">
         <v>592.998505179033</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>55.615316810403954</v>
+        <v>55.362368061570962</v>
       </c>
       <c r="B37">
-        <v>-35.934357271706347</v>
+        <v>-36.324331513404225</v>
       </c>
       <c r="C37">
         <v>592.998505179033</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>58.6763588045037</v>
+        <v>58.469142024140822</v>
       </c>
       <c r="B38">
-        <v>-38.8199619801817</v>
+        <v>-39.139430675567262</v>
       </c>
       <c r="C38">
         <v>592.998505179033</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>61.720430484794704</v>
+        <v>61.559905317266079</v>
       </c>
       <c r="B39">
-        <v>-41.731730033166478</v>
+        <v>-41.979213686551674</v>
       </c>
       <c r="C39">
         <v>592.998505179033</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>64.736912686861274</v>
+        <v>64.6264234064904</v>
       </c>
       <c r="B40">
-        <v>-44.686033128918005</v>
+        <v>-44.8563758308573</v>
       </c>
       <c r="C40">
         <v>592.998505179033</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>67.715186246287729</v>
+        <v>67.66046175735751</v>
       </c>
       <c r="B41">
-        <v>-47.699242965693664</v>
+        <v>-47.783612392984075</v>
       </c>
       <c r="C41">
         <v>592.998505179033</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>67.228746344685831</v>
+        <v>67.283470833616036</v>
       </c>
       <c r="B42">
-        <v>-48.449193430497282</v>
+        <v>-48.36482400320687</v>
       </c>
       <c r="C42">
         <v>592.998505179033</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>63.7547857502313</v>
+        <v>63.86527503060217</v>
       </c>
       <c r="B43">
-        <v>-46.200190479489507</v>
+        <v>-46.029847777550216</v>
       </c>
       <c r="C43">
         <v>592.998505179033</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>60.293540106762457</v>
+        <v>60.454065274291082</v>
       </c>
       <c r="B44">
-        <v>-43.931584729923742</v>
+        <v>-43.684101076538553</v>
       </c>
       <c r="C44">
         <v>592.998505179033</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>56.834431867944843</v>
+        <v>57.041648648307714</v>
       </c>
       <c r="B45">
-        <v>-41.659683716942283</v>
+        <v>-41.340215021556723</v>
       </c>
       <c r="C45">
         <v>592.998505179033</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>53.366883487444049</v>
+        <v>53.619832236277034</v>
       </c>
       <c r="B46">
-        <v>-39.400794975687489</v>
+        <v>-39.010820733989611</v>
       </c>
       <c r="C46">
         <v>592.998505179033</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>49.884834725083138</v>
+        <v>50.183923910245369</v>
       </c>
       <c r="B47">
-        <v>-37.164261654043656</v>
+        <v>-36.703152126039264</v>
       </c>
       <c r="C47">
         <v>592.998505179033</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>46.400294565315292</v>
+        <v>46.743234695944629</v>
       </c>
       <c r="B48">
-        <v>-34.931569350863121</v>
+        <v>-34.402854273176565</v>
       </c>
       <c r="C48">
         <v>592.998505179033</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>42.925905432103889</v>
+        <v>43.30756634997104</v>
       </c>
       <c r="B49">
-        <v>-32.68322708340294</v>
+        <v>-32.094815684976808</v>
       </c>
       <c r="C49">
         <v>592.998505179033</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>39.458774282823086</v>
+        <v>39.874680398692711</v>
       </c>
       <c r="B50">
-        <v>-30.423695091571179</v>
+        <v>-29.78248744416409</v>
       </c>
       <c r="C50">
         <v>592.998505179033</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>35.993219071675135</v>
+        <v>36.44017667934942</v>
       </c>
       <c r="B51">
-        <v>-28.161733456259622</v>
+        <v>-27.472653336559318</v>
       </c>
       <c r="C51">
         <v>592.998505179033</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>32.527937206764264</v>
+        <v>33.003048502896142</v>
       </c>
       <c r="B52">
-        <v>-25.899350399644231</v>
+        <v>-25.166865387221979</v>
       </c>
       <c r="C52">
         <v>592.998505179033</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>29.062720959670248</v>
+        <v>29.563137548716693</v>
       </c>
       <c r="B53">
-        <v>-23.636866179222071</v>
+        <v>-22.865367681021251</v>
       </c>
       <c r="C53">
         <v>592.998505179033</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>25.597362601972748</v>
+        <v>26.120285496194789</v>
       </c>
       <c r="B54">
-        <v>-21.374601052490124</v>
+        <v>-20.568404302826242</v>
       </c>
       <c r="C54">
         <v>592.998505179033</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>22.131638750937189</v>
+        <v>22.674321709272011</v>
       </c>
       <c r="B55">
-        <v>-19.112899411397109</v>
+        <v>-18.276238324377012</v>
       </c>
       <c r="C55">
         <v>592.998505179033</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>18.665263406571682</v>
+        <v>19.225026290121026</v>
       </c>
       <c r="B56">
-        <v>-16.852202185698513</v>
+        <v>-15.989208764897283</v>
       </c>
       <c r="C56">
         <v>592.998505179033</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>15.197934914569977</v>
+        <v>15.772167025472253</v>
       </c>
       <c r="B57">
-        <v>-14.592974439601461</v>
+        <v>-13.70767363048166</v>
       </c>
       <c r="C57">
         <v>592.998505179033</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>11.72935162062586</v>
+        <v>12.315511702056151</v>
       </c>
       <c r="B58">
-        <v>-12.335681237313132</v>
+        <v>-11.43199092722478</v>
       </c>
       <c r="C58">
         <v>592.998505179033</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>8.2593359832077855</v>
+        <v>8.8549241203305922</v>
       </c>
       <c r="B59">
-        <v>-10.080596296827546</v>
+        <v>-9.162370635659828</v>
       </c>
       <c r="C59">
         <v>592.998505179033</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>4.788206911883079</v>
+        <v>5.3906521356633039</v>
       </c>
       <c r="B60">
-        <v>-7.8272279512863143</v>
+        <v>-6.8984306340743542</v>
       </c>
       <c r="C60">
         <v>592.998505179033</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1.3164074289937155</v>
+        <v>1.9230396171494133</v>
       </c>
       <c r="B61">
-        <v>-5.5748931876178993</v>
+        <v>-4.6396407751944633</v>
       </c>
       <c r="C61">
         <v>592.998505179033</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-2.1556194431182902</v>
+        <v>-1.5475695661159135</v>
       </c>
       <c r="B62">
-        <v>-3.3229089927507927</v>
+        <v>-2.3854709117462778</v>
       </c>
       <c r="C62">
         <v>592.998505179033</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-5.6275783562249266</v>
+        <v>-5.0209461680692291</v>
       </c>
       <c r="B63">
-        <v>-1.07082002463732</v>
+        <v>-0.13556761221388339</v>
       </c>
       <c r="C63">
         <v>592.998505179033</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-9.0997646585542178</v>
+        <v>-8.497319434773992</v>
       </c>
       <c r="B64">
-        <v>1.1809183746748537</v>
+        <v>2.1097156918868127</v>
       </c>
       <c r="C64">
         <v>592.998505179033</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-12.572621372448142</v>
+        <v>-11.977033235325333</v>
       </c>
       <c r="B65">
-        <v>3.431623192114194</v>
+        <v>4.3498488532819124</v>
       </c>
       <c r="C65">
         <v>592.998505179033</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-16.046591520248722</v>
+        <v>-15.46043143881843</v>
       </c>
       <c r="B66">
-        <v>5.6806114146091966</v>
+        <v>6.584301724697549</v>
       </c>
       <c r="C66">
         <v>592.998505179033</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-19.521994011523248</v>
+        <v>-18.947761900620971</v>
       </c>
       <c r="B67">
-        <v>7.9273913753014451</v>
+        <v>8.8126921844212482</v>
       </c>
       <c r="C67">
         <v>592.998505179033</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-22.998651304740182</v>
+        <v>-22.438888421190839</v>
       </c>
       <c r="B68">
-        <v>10.172236792184975</v>
+        <v>11.035230212986205</v>
       </c>
       <c r="C68">
         <v>592.998505179033</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-26.476261745593309</v>
+        <v>-25.93357878725849</v>
       </c>
       <c r="B69">
-        <v>12.415612729466956</v>
+        <v>13.252273816487055</v>
       </c>
       <c r="C69">
         <v>592.998505179033</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-29.954523679776397</v>
+        <v>-29.431600785554355</v>
       </c>
       <c r="B70">
-        <v>14.657984251354526</v>
+        <v>15.46418100101841</v>
       </c>
       <c r="C70">
         <v>592.998505179033</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-33.433151107297554</v>
+        <v>-32.93273451825111</v>
       </c>
       <c r="B71">
-        <v>16.899792287603159</v>
+        <v>17.671290785803979</v>
       </c>
       <c r="C71">
         <v>592.998505179033</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-36.911920645422164</v>
+        <v>-36.436809349290286</v>
       </c>
       <c r="B72">
-        <v>19.141381230161578</v>
+        <v>19.873866242583826</v>
       </c>
       <c r="C72">
         <v>592.998505179033</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-40.390624565729951</v>
+        <v>-39.943666958055665</v>
       </c>
       <c r="B73">
-        <v>21.383071336526775</v>
+        <v>22.072151456227079</v>
       </c>
       <c r="C73">
         <v>592.998505179033</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-43.869055139800643</v>
+        <v>-43.453149023931012</v>
       </c>
       <c r="B74">
-        <v>23.625182864195793</v>
+        <v>24.266390511602882</v>
       </c>
       <c r="C74">
         <v>592.998505179033</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-47.34590977573847</v>
+        <v>-46.964248857871326</v>
       </c>
       <c r="B75">
-        <v>25.869724035344611</v>
+        <v>26.458135433770742</v>
       </c>
       <c r="C75">
         <v>592.998505179033</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-50.815506427745731</v>
+        <v>-50.472566297116387</v>
       </c>
       <c r="B76">
-        <v>28.125454930865018</v>
+        <v>28.654170008551564</v>
       </c>
       <c r="C76">
         <v>592.998505179033</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-54.274952053196515</v>
+        <v>-53.975862868034284</v>
       </c>
       <c r="B77">
-        <v>30.396835790665062</v>
+        <v>30.857945318669451</v>
       </c>
       <c r="C77">
         <v>592.998505179033</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-57.736889076054247</v>
+        <v>-57.483940327221262</v>
       </c>
       <c r="B78">
-        <v>32.6643756320018</v>
+        <v>33.054349873699678</v>
       </c>
       <c r="C78">
         <v>592.998505179033</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-61.213326480772089</v>
+        <v>-61.006109700409219</v>
       </c>
       <c r="B79">
-        <v>34.909560053727574</v>
+        <v>35.229028749113141</v>
       </c>
       <c r="C79">
         <v>592.998505179033</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-64.698204027173134</v>
+        <v>-64.537678859644515</v>
       </c>
       <c r="B80">
-        <v>37.141732203726725</v>
+        <v>37.389215857111921</v>
       </c>
       <c r="C80">
         <v>592.998505179033</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-68.18094416892292</v>
+        <v>-68.07045488855205</v>
       </c>
       <c r="B81">
-        <v>39.377199617141535</v>
+        <v>39.547542319080826</v>
       </c>
       <c r="C81">
         <v>592.998505179033</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-71.650969359687039</v>
+        <v>-71.596244870756834</v>
       </c>
       <c r="B82">
-        <v>41.632269829114342</v>
+        <v>41.716639256404747</v>
       </c>
       <c r="C82">
         <v>592.998505179033</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-86.2701906983153</v>
+        <v>-86.297190149774522</v>
       </c>
       <c r="B1">
-        <v>29.984892216091325</v>
+        <v>29.907255563235665</v>
       </c>
       <c r="C1">
         <v>767.45943045334911</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-81.855602656835842</v>
+        <v>-81.910367283356834</v>
       </c>
       <c r="B2">
-        <v>28.7733778074899</v>
+        <v>28.616715630479085</v>
       </c>
       <c r="C2">
         <v>767.45943045334911</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-77.4507458141711</v>
+        <v>-77.530423206084308</v>
       </c>
       <c r="B3">
-        <v>27.534166361672622</v>
+        <v>27.306597217970875</v>
       </c>
       <c r="C3">
         <v>767.45943045334911</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-73.052058226317314</v>
+        <v>-73.154983276309508</v>
       </c>
       <c r="B4">
-        <v>26.277395919954952</v>
+        <v>25.983659054962583</v>
       </c>
       <c r="C4">
         <v>767.45943045334911</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-68.655977949270735</v>
+        <v>-68.781672852385114</v>
       </c>
       <c r="B5">
-        <v>25.013204523652377</v>
+        <v>24.654659870705775</v>
       </c>
       <c r="C5">
         <v>767.45943045334911</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-64.26046140624554</v>
+        <v>-64.409129537789752</v>
       </c>
       <c r="B6">
-        <v>23.7474086218344</v>
+        <v>23.323477332060751</v>
       </c>
       <c r="C6">
         <v>767.45943045334911</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-59.869538489327468</v>
+        <v>-60.040039916506153</v>
       </c>
       <c r="B7">
-        <v>22.468538294586633</v>
+        <v>21.982464856322668</v>
       </c>
       <c r="C7">
         <v>767.45943045334911</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-55.487452255037553</v>
+        <v>-55.677232682610807</v>
       </c>
       <c r="B8">
-        <v>21.164516911207325</v>
+        <v>20.623571385590104</v>
       </c>
       <c r="C8">
         <v>767.45943045334911</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-51.113224948765968</v>
+        <v>-51.320055990050847</v>
       </c>
       <c r="B9">
-        <v>19.838127366829045</v>
+        <v>19.2486522107402</v>
       </c>
       <c r="C9">
         <v>767.45943045334911</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-46.744941802432876</v>
+        <v>-46.967233317676545</v>
       </c>
       <c r="B10">
-        <v>18.494819493869848</v>
+        <v>17.861340579275531</v>
       </c>
       <c r="C10">
         <v>767.45943045334911</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-42.382160805209089</v>
+        <v>-42.618469984080008</v>
       </c>
       <c r="B11">
-        <v>17.135851348055365</v>
+        <v>16.462475216421705</v>
       </c>
       <c r="C11">
         <v>767.45943045334911</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-38.024808135578041</v>
+        <v>-38.273716767788812</v>
       </c>
       <c r="B12">
-        <v>15.761433040938147</v>
+        <v>15.052196216835085</v>
       </c>
       <c r="C12">
         <v>767.45943045334911</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-33.672809972023209</v>
+        <v>-33.932924447330493</v>
       </c>
       <c r="B13">
-        <v>14.371774684070727</v>
+        <v>13.630643675172051</v>
       </c>
       <c r="C13">
         <v>767.45943045334911</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-29.32608750723298</v>
+        <v>-29.596040477855126</v>
       </c>
       <c r="B14">
-        <v>12.967100579626395</v>
+        <v>12.197967145119918</v>
       </c>
       <c r="C14">
         <v>767.45943045334911</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-24.984541990715417</v>
+        <v>-25.262999021002663</v>
       </c>
       <c r="B15">
-        <v>11.547691792261377</v>
+        <v>10.754354016489772</v>
       </c>
       <c r="C15">
         <v>767.45943045334911</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-20.648069686183558</v>
+        <v>-20.933730915035596</v>
       </c>
       <c r="B16">
-        <v>10.113843577252654</v>
+        <v>9.3000011381236618</v>
       </c>
       <c r="C16">
         <v>767.45943045334911</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-16.316566857350388</v>
+        <v>-16.608166998216372</v>
       </c>
       <c r="B17">
-        <v>8.6658511898771931</v>
+        <v>7.8351053588636148</v>
       </c>
       <c r="C17">
         <v>767.45943045334911</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-11.989971740700282</v>
+        <v>-12.286266091120936</v>
       </c>
       <c r="B18">
-        <v>7.2038904220824955</v>
+        <v>6.3597838840059708</v>
       </c>
       <c r="C18">
         <v>767.45943045334911</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-7.6683904638030249</v>
+        <v>-7.9680989435791085</v>
       </c>
       <c r="B19">
-        <v>5.7276592124981471</v>
+        <v>4.8738353446642533</v>
       </c>
       <c r="C19">
         <v>767.45943045334911</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-3.3519711269997421</v>
+        <v>-3.6537642877341718</v>
       </c>
       <c r="B20">
-        <v>4.236736036424257</v>
+        <v>3.3769787284062867</v>
       </c>
       <c r="C20">
         <v>767.45943045334911</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>0.95913816936842178</v>
+        <v>0.65663914427057746</v>
       </c>
       <c r="B21">
-        <v>2.7306993691609378</v>
+        <v>1.8689330227998928</v>
       </c>
       <c r="C21">
         <v>767.45943045334911</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>5.26483869174074</v>
+        <v>4.96304553100631</v>
       </c>
       <c r="B22">
-        <v>1.2092681942415835</v>
+        <v>0.34951088622361265</v>
       </c>
       <c r="C22">
         <v>767.45943045334911</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>9.5652291736779524</v>
+        <v>9.26552069390187</v>
       </c>
       <c r="B23">
-        <v>-0.32727647186720549</v>
+        <v>-1.1811003397010984</v>
       </c>
       <c r="C23">
         <v>767.45943045334911</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>13.860457715521193</v>
+        <v>13.564163365100537</v>
       </c>
       <c r="B24">
-        <v>-1.8785131044655352</v>
+        <v>-2.7226196425420612</v>
       </c>
       <c r="C24">
         <v>767.45943045334911</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>18.150672417611585</v>
+        <v>17.8590722767456</v>
       </c>
       <c r="B25">
-        <v>-3.4440201788535165</v>
+        <v>-4.2747660098670961</v>
       </c>
       <c r="C25">
         <v>767.45943045334911</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>22.435979407518897</v>
+        <v>22.150318178666854</v>
       </c>
       <c r="B26">
-        <v>-5.0234956336607288</v>
+        <v>-5.8373380727897226</v>
       </c>
       <c r="C26">
         <v>767.45943045334911</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>26.716316921727504</v>
+        <v>26.437859891440258</v>
       </c>
       <c r="B27">
-        <v>-6.6171152608346757</v>
+        <v>-7.41045303660628</v>
       </c>
       <c r="C27">
         <v>767.45943045334911</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>30.99158122395044</v>
+        <v>30.721628253328291</v>
       </c>
       <c r="B28">
-        <v>-8.2251743156523354</v>
+        <v>-8.9943077501588142</v>
       </c>
       <c r="C28">
         <v>767.45943045334911</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>35.261668577900686</v>
+        <v>35.0015541025934</v>
       </c>
       <c r="B29">
-        <v>-9.8479680533906784</v>
+        <v>-10.589099062289355</v>
       </c>
       <c r="C29">
         <v>767.45943045334911</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>39.526480233086367</v>
+        <v>39.277571600875596</v>
       </c>
       <c r="B30">
-        <v>-11.485777538705943</v>
+        <v>-12.195014362809006</v>
       </c>
       <c r="C30">
         <v>767.45943045334911</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>43.785937382195776</v>
+        <v>43.549628203324858</v>
       </c>
       <c r="B31">
-        <v>-13.138827073771386</v>
+        <v>-13.812203205405053</v>
       </c>
       <c r="C31">
         <v>767.45943045334911</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>48.039966203712495</v>
+        <v>47.817674688468827</v>
       </c>
       <c r="B32">
-        <v>-14.807326770139591</v>
+        <v>-15.440805684733903</v>
       </c>
       <c r="C32">
         <v>767.45943045334911</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>52.288492876119882</v>
+        <v>52.08166183483501</v>
       </c>
       <c r="B33">
-        <v>-16.491486739363065</v>
+        <v>-17.080961895451907</v>
       </c>
       <c r="C33">
         <v>767.45943045334911</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>56.5310753885888</v>
+        <v>56.341294961015542</v>
       </c>
       <c r="B34">
-        <v>-18.192565037167466</v>
+        <v>-18.733510562784684</v>
       </c>
       <c r="C34">
         <v>767.45943045334911</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>60.765798973039352</v>
+        <v>60.595297545860667</v>
       </c>
       <c r="B35">
-        <v>-19.916011495970832</v>
+        <v>-20.402084934234789</v>
       </c>
       <c r="C35">
         <v>767.45943045334911</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>64.991685874861787</v>
+        <v>64.843017743317574</v>
       </c>
       <c r="B36">
-        <v>-21.664609010905739</v>
+        <v>-22.088540300679387</v>
       </c>
       <c r="C36">
         <v>767.45943045334911</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>69.21297915057707</v>
+        <v>69.087284247462719</v>
       </c>
       <c r="B37">
-        <v>-23.426280951270442</v>
+        <v>-23.784825604217041</v>
       </c>
       <c r="C37">
         <v>767.45943045334911</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>73.433708692271</v>
+        <v>73.3307836422788</v>
       </c>
       <c r="B38">
-        <v>-25.189557397150541</v>
+        <v>-25.483294262142909</v>
       </c>
       <c r="C38">
         <v>767.45943045334911</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>77.6518309231577</v>
+        <v>77.57215353124451</v>
       </c>
       <c r="B39">
-        <v>-26.960254797615551</v>
+        <v>-27.187823941317298</v>
       </c>
       <c r="C39">
         <v>767.45943045334911</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>81.863783899233454</v>
+        <v>81.809019272712447</v>
       </c>
       <c r="B40">
-        <v>-28.748511193980946</v>
+        <v>-28.905173370991758</v>
       </c>
       <c r="C40">
         <v>767.45943045334911</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>86.066005676494456</v>
+        <v>86.039006225035237</v>
       </c>
       <c r="B41">
-        <v>-30.564464627562192</v>
+        <v>-30.642101280417855</v>
       </c>
       <c r="C41">
         <v>767.45943045334911</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>85.902522413016584</v>
+        <v>85.930017382716656</v>
       </c>
       <c r="B42">
-        <v>-31.029772357774178</v>
+        <v>-30.95230643389251</v>
       </c>
       <c r="C42">
         <v>767.45943045334911</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>81.533709585384926</v>
+        <v>81.588969730146772</v>
       </c>
       <c r="B43">
-        <v>-29.68797206912383</v>
+        <v>-29.531480621087013</v>
       </c>
       <c r="C43">
         <v>767.45943045334911</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>77.17228001695598</v>
+        <v>77.252452927110028</v>
       </c>
       <c r="B44">
-        <v>-28.325157472904046</v>
+        <v>-28.097759058176294</v>
       </c>
       <c r="C44">
         <v>767.45943045334911</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>72.814671837595242</v>
+        <v>72.91809240582829</v>
       </c>
       <c r="B45">
-        <v>-26.951466400182792</v>
+        <v>-26.657900264164411</v>
       </c>
       <c r="C45">
         <v>767.45943045334911</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>68.457323177168277</v>
+        <v>68.58351359852351</v>
       </c>
       <c r="B46">
-        <v>-25.577036682028066</v>
+        <v>-25.218662758055455</v>
       </c>
       <c r="C46">
         <v>767.45943045334911</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>64.098190530873978</v>
+        <v>64.24735418065903</v>
       </c>
       <c r="B47">
-        <v>-24.207684562625648</v>
+        <v>-23.783924001825994</v>
       </c>
       <c r="C47">
         <v>767.45943045334911</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>59.74130385524473</v>
+        <v>59.912300800664262</v>
       </c>
       <c r="B48">
-        <v>-22.831939938632608</v>
+        <v>-22.346037229342645</v>
       </c>
       <c r="C48">
         <v>767.45943045334911</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>55.390906268426754</v>
+        <v>55.581182214240854</v>
       </c>
       <c r="B49">
-        <v>-21.437726003948811</v>
+        <v>-20.896951207305587</v>
       </c>
       <c r="C49">
         <v>767.45943045334911</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>51.046020073688112</v>
+        <v>51.25334663321383</v>
       </c>
       <c r="B50">
-        <v>-20.027825488974159</v>
+        <v>-19.4385210618593</v>
       </c>
       <c r="C50">
         <v>767.45943045334911</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>46.704730557527981</v>
+        <v>46.927517591012489</v>
       </c>
       <c r="B51">
-        <v>-18.607688070783507</v>
+        <v>-17.974379885163181</v>
       </c>
       <c r="C51">
         <v>767.45943045334911</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>42.366595754247683</v>
+        <v>42.603400451359455</v>
       </c>
       <c r="B52">
-        <v>-17.178571676651394</v>
+        <v>-16.505366273991726</v>
       </c>
       <c r="C52">
         <v>767.45943045334911</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>38.031541885099223</v>
+        <v>38.280946035550834</v>
       </c>
       <c r="B53">
-        <v>-15.740686296402338</v>
+        <v>-15.031620201273267</v>
       </c>
       <c r="C53">
         <v>767.45943045334911</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>33.699495171334426</v>
+        <v>33.960105164882563</v>
       </c>
       <c r="B54">
-        <v>-14.294241919860767</v>
+        <v>-13.553281639936083</v>
       </c>
       <c r="C54">
         <v>767.45943045334911</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>29.370376845495009</v>
+        <v>29.640825334358006</v>
       </c>
       <c r="B55">
-        <v>-12.839462735769226</v>
+        <v>-12.070500030236742</v>
       </c>
       <c r="C55">
         <v>767.45943045334911</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>25.044088185281481</v>
+        <v>25.323040733809577</v>
       </c>
       <c r="B56">
-        <v>-11.376629728542323</v>
+        <v>-10.583462681744713</v>
       </c>
       <c r="C56">
         <v>767.45943045334911</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>20.72052547968411</v>
+        <v>21.006682226776995</v>
       </c>
       <c r="B57">
-        <v>-9.9060380815127065</v>
+        <v>-9.0923663713577056</v>
       </c>
       <c r="C57">
         <v>767.45943045334911</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>16.399585017693127</v>
+        <v>16.691680676799958</v>
       </c>
       <c r="B58">
-        <v>-8.4279829780130129</v>
+        <v>-7.5974078759734258</v>
       </c>
       <c r="C58">
         <v>767.45943045334911</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>12.081205058274721</v>
+        <v>12.377994926936221</v>
       </c>
       <c r="B59">
-        <v>-6.9426401460027112</v>
+        <v>-6.0987043369001794</v>
       </c>
       <c r="C59">
         <v>767.45943045334911</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>7.765491740298903</v>
+        <v>8.065695738315835</v>
       </c>
       <c r="B60">
-        <v>-5.4497074919485931</v>
+        <v>-4.59605435308869</v>
       </c>
       <c r="C60">
         <v>767.45943045334911</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3.45259317261162</v>
+        <v>3.7548818515868962</v>
       </c>
       <c r="B61">
-        <v>-3.9487634669442691</v>
+        <v>-3.0891768879002894</v>
       </c>
       <c r="C61">
         <v>767.45943045334911</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-0.85734253594118337</v>
+        <v>-0.55434799260249257</v>
       </c>
       <c r="B62">
-        <v>-2.4393865220833537</v>
+        <v>-1.5777909046963015</v>
       </c>
       <c r="C62">
         <v>767.45943045334911</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-5.1642166461288621</v>
+        <v>-4.8619279671535862</v>
       </c>
       <c r="B63">
-        <v>-0.92129562476159477</v>
+        <v>-0.061709045717615742</v>
       </c>
       <c r="C63">
         <v>767.45943045334911</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-9.4681278971820753</v>
+        <v>-9.1679238991651424</v>
       </c>
       <c r="B64">
-        <v>0.60522819241675985</v>
+        <v>1.4588813312766618</v>
       </c>
       <c r="C64">
         <v>767.45943045334911</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-13.769224397946754</v>
+        <v>-13.472434529285252</v>
       </c>
       <c r="B65">
-        <v>2.1397633805453187</v>
+        <v>2.9836991896478522</v>
       </c>
       <c r="C65">
         <v>767.45943045334911</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-18.067654257268845</v>
+        <v>-17.775558598162014</v>
       </c>
       <c r="B66">
-        <v>3.6818883907176962</v>
+        <v>4.5124634927572833</v>
       </c>
       <c r="C66">
         <v>767.45943045334911</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-22.363523614018344</v>
+        <v>-22.077366866925455</v>
       </c>
       <c r="B67">
-        <v>5.2313011294006788</v>
+        <v>6.0449728395556779</v>
       </c>
       <c r="C67">
         <v>767.45943045334911</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-26.65677072716144</v>
+        <v>-26.377818178633344</v>
       </c>
       <c r="B68">
-        <v>6.7881773245537307</v>
+        <v>7.58134437135134</v>
       </c>
       <c r="C68">
         <v>767.45943045334911</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-30.947291885688411</v>
+        <v>-30.676843396825412</v>
       </c>
       <c r="B69">
-        <v>8.3528121595095044</v>
+        <v>9.12177486504199</v>
       </c>
       <c r="C69">
         <v>767.45943045334911</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-35.234983378589469</v>
+        <v>-34.974373385041332</v>
       </c>
       <c r="B70">
-        <v>9.92550081760064</v>
+        <v>10.666461097525323</v>
       </c>
       <c r="C70">
         <v>767.45943045334911</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-39.519746483565186</v>
+        <v>-39.270342333113568</v>
       </c>
       <c r="B71">
-        <v>11.506524283241756</v>
+        <v>12.215590378370823</v>
       </c>
       <c r="C71">
         <v>767.45943045334911</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-43.801502433157182</v>
+        <v>-43.56469773604541</v>
       </c>
       <c r="B72">
-        <v>13.096106745175359</v>
+        <v>13.769312147835031</v>
       </c>
       <c r="C72">
         <v>767.45943045334911</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-48.080177448617391</v>
+        <v>-47.857390415132876</v>
       </c>
       <c r="B73">
-        <v>14.69445819322593</v>
+        <v>15.327766378846253</v>
       </c>
       <c r="C73">
         <v>767.45943045334911</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-52.355697751197745</v>
+        <v>-52.148371191672027</v>
       </c>
       <c r="B74">
-        <v>16.301788617217952</v>
+        <v>16.891093044332806</v>
       </c>
       <c r="C74">
         <v>767.45943045334911</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-56.627621375199595</v>
+        <v>-56.4373454293855</v>
       </c>
       <c r="B75">
-        <v>17.919355944425977</v>
+        <v>18.460130741069204</v>
       </c>
       <c r="C75">
         <v>767.45943045334911</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-60.89403360712209</v>
+        <v>-60.723036661702565</v>
       </c>
       <c r="B76">
-        <v>19.552609851924849</v>
+        <v>20.038512561214816</v>
       </c>
       <c r="C76">
         <v>767.45943045334911</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-65.153956750233348</v>
+        <v>-65.0047931004483</v>
       </c>
       <c r="B77">
-        <v>21.20433307011449</v>
+        <v>21.628093630914144</v>
       </c>
       <c r="C77">
         <v>767.45943045334911</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-69.411633922679528</v>
+        <v>-69.285443501324323</v>
       </c>
       <c r="B78">
-        <v>22.86244879289475</v>
+        <v>23.22082271686736</v>
       </c>
       <c r="C78">
         <v>767.45943045334911</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-73.671095080993069</v>
+        <v>-73.567674512760021</v>
       </c>
       <c r="B79">
-        <v>24.5154869169227</v>
+        <v>24.809053052941081</v>
       </c>
       <c r="C79">
         <v>767.45943045334911</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-77.930296720372837</v>
+        <v>-77.85012381021879</v>
       </c>
       <c r="B80">
-        <v>26.169263686384127</v>
+        <v>26.396662101111879</v>
       </c>
       <c r="C80">
         <v>767.45943045334911</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-82.185676970684355</v>
+        <v>-82.130416825922509</v>
       </c>
       <c r="B81">
-        <v>27.833916932347012</v>
+        <v>27.99040838038383</v>
       </c>
       <c r="C81">
         <v>767.45943045334911</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-86.433673961793176</v>
+        <v>-86.4061789920931</v>
       </c>
       <c r="B82">
-        <v>29.519584485879339</v>
+        <v>29.597050409761007</v>
       </c>
       <c r="C82">
         <v>767.45943045334911</v>
